--- a/Luban/Config/Datas/Levels/L09/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L09/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L9 W1/25; N=39; EHP=228.228000; normal:17x19,normal:18x20</t>
+          <t>L9 W1/25; N=39; EHP=478.433795; normal:17x19,normal:18x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L9 W2/25; N=45; EHP=275.743314; normal:17x23,normal:18x22</t>
+          <t>L9 W2/25; N=45; EHP=578.040031; normal:17x23,normal:18x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3424136,3424673,3424019,3424136,3424673,3424091,3424136,3424673,3424099,3424136,3424673,3424099,3424136,3424673,3424107,3424136,3424673,3424115,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144</t>
+          <t>3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424673,3424136,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144,3424144</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L9 W3/25; N=51; EHP=345.726797; air:2x1,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x15,normal:18x16,swarm:84x14</t>
+          <t>L9 W3/25; N=51; EHP=780.626201; normal:17x15,normal:18x22,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3426136,3426673,3426019,3426136,3426673,3426019,3426136,3426673,3426091,3426136,3426673,3426099,3426136,3426673,3426107,3426136,3426673,3426107,3426136,3426673,3426115,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426136,3426136,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144</t>
+          <t>3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426673,3426136,3426136,3426136,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426144,3426136,3426136,3426136,3426136,3426136,3426136,3426136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L9 W4/25; N=57; EHP=444.941020; air:2x2,air:11x1,air:12x1,air:13x2,air:14x1,normal:17x18,normal:18x17,swarm:84x15</t>
+          <t>L9 W4/25; N=57; EHP=1007.697570; normal:17x25,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3428136,3428673,3428019,3428668,3428136,3428673,3428091,3428668,3428136,3428673,3428091,3428668,3428136,3428673,3428099,3428868,3428136,3428673,3428107,3428868,3428136,3428673,3428107,3428868,3428136,3428673,3428115,3428988,3428136,3428673,3428115,3428988,3428136,3428673,3428988,3428136,3428673,3428136,3428673,3428136,3428673,3428136,3428673,3428136,3428673,3428144,3428673,3428144,3428673,3428144,3428673,3428144,3428144,3428144,3428144,3428144,3428144,3428144,3428144,3428144,3428144,3428144,3428144</t>
+          <t>3428136,3428019,3428019,3428668,3428136,3428091,3428091,3428668,3428136,3428091,3428091,3428668,3428136,3428099,3428099,3428868,3428136,3428107,3428107,3428868,3428136,3428107,3428107,3428868,3428136,3428115,3428115,3428988,3428136,3428115,3428115,3428988,3428136,3428673,3428988,3428136,3428673,3428136,3428673,3428136,3428673,3428136,3428673,3428136,3428673,3428144,3428673,3428144,3428673,3428144,3428673,3428144,3428144,3428144,3428144,3428144,3428144,3428144,3428144,3428144,3428144,3428144,3428144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L9 W5/25; N=63; EHP=847.016888; air:2x1,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x14,normal:18x15,medium:83x3,swarm:84x17,medium:108x3,medium:123x3</t>
+          <t>L9 W5/25; N=63; EHP=1799.695766; air:2x2,air:11x4,air:12x2,air:13x4,air:14x4,medium:83x3,medium:108x3,medium:123x3,normal:17x14,normal:18x15,swarm:84x9 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3430136,3430673,3430242,3430019,3430668,3430136,3430673,3430242,3430091,3430668,3430136,3430673,3430242,3430091,3430668,3430136,3430673,3430466,3430099,3430668,3430136,3430673,3430466,3430099,3430868,3430136,3430673,3430786,3430107,3430868,3430136,3430673,3430786,3430115,3430868,3430136,3430673,3430786,3430115,3430988,3430136,3430673,3430988,3430136,3430673,3430988,3430136,3430673,3430136,3430673,3430144,3430673,3430144,3430673,3430144,3430673,3430144,3430673,3430144,3430673,3430144,3430673,3430144,3430673,3430144,3430144,3430144,3430144,3430144</t>
+          <t>3430136,3430019,3430242,3430019,3430668,3430136,3430091,3430242,3430091,3430668,3430136,3430091,3430242,3430091,3430668,3430136,3430099,3430466,3430099,3430668,3430136,3430099,3430466,3430099,3430868,3430136,3430107,3430786,3430107,3430868,3430136,3430115,3430786,3430115,3430868,3430136,3430115,3430786,3430115,3430988,3430136,3430673,3430988,3430136,3430673,3430988,3430136,3430673,3430136,3430673,3430144,3430673,3430144,3430673,3430144,3430673,3430144,3430673,3430144,3430673,3430144,3430673,3430144,3430673,3430144,3430144,3430144,3430144,3430144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L9 W6/25; N=69; EHP=864.000000; air:2x1,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x12,normal:18x12,fast:30x3,fast:58x2,medium:83x4,swarm:84x19,fast:98x3,medium:108x3,medium:123x3</t>
+          <t>L9 W6/25; N=69; EHP=1833.929874; air:2x2,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x3,fast:58x2,fast:98x3,medium:83x4,medium:108x3,medium:123x3,normal:17x12,normal:18x12,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3432136,3432673,3432242,3432019,3432668,3432136,3432673,3432242,3432019,3432668,3432136,3432673,3432242,3432091,3432668,3432136,3432673,3432466,3432099,3432868,3432136,3432673,3432466,3432099,3432868,3432136,3432673,3432466,3432107,3432868,3432136,3432673,3432786,3432107,3432868,3432136,3432673,3432786,3432115,3432988,3432136,3432673,3432786,3432115,3432988,3432136,3432673,3432988,3432136,3432673,3432988,3432136,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432144,3432144,3432144</t>
+          <t>3432136,3432019,3432242,3432019,3432668,3432136,3432019,3432242,3432019,3432668,3432136,3432091,3432242,3432091,3432668,3432136,3432099,3432466,3432099,3432868,3432136,3432099,3432466,3432099,3432868,3432136,3432107,3432466,3432107,3432868,3432136,3432107,3432786,3432107,3432868,3432136,3432115,3432786,3432115,3432988,3432136,3432115,3432786,3432115,3432988,3432136,3432673,3432988,3432136,3432673,3432988,3432136,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432673,3432144,3432144,3432144,3432144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L9 W7/25; N=75; EHP=985.593840; air:2x2,air:11x1,air:12x2,air:13x2,air:14x2,normal:17x12,normal:18x13,fast:30x3,fast:58x3,medium:83x3,swarm:84x21,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L9 W7/25; N=75; EHP=2093.027533; air:2x4,air:11x2,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:98x3,medium:83x3,medium:108x4,medium:123x4,normal:17x12,normal:18x13,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3434136,3434673,3434242,3434019,3434668,3434136,3434673,3434242,3434019,3434668,3434136,3434673,3434242,3434091,3434668,3434136,3434673,3434466,3434091,3434668,3434136,3434673,3434466,3434099,3434868,3434136,3434673,3434466,3434099,3434868,3434136,3434673,3434786,3434107,3434868,3434136,3434673,3434786,3434107,3434868,3434136,3434673,3434786,3434115,3434988,3434136,3434673,3434115,3434988,3434136,3434673,3434988,3434136,3434673,3434988,3434136,3434673,3434136,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434144,3434144,3434144,3434144,3434144</t>
+          <t>3434136,3434019,3434242,3434019,3434668,3434136,3434019,3434242,3434019,3434668,3434136,3434091,3434242,3434091,3434668,3434136,3434091,3434466,3434091,3434668,3434136,3434099,3434466,3434099,3434868,3434136,3434099,3434466,3434099,3434868,3434136,3434107,3434786,3434107,3434868,3434136,3434107,3434786,3434107,3434868,3434136,3434115,3434786,3434115,3434988,3434136,3434115,3434115,3434988,3434136,3434673,3434988,3434136,3434673,3434988,3434136,3434673,3434136,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434673,3434144,3434144,3434144,3434144,3434144,3434144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L9 W8/25; N=81; EHP=1270.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x14,fast:30x3,fast:58x3,medium:83x4,swarm:84x22,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L9 W8/25; N=81; EHP=2697.866320; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:98x3,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3436136,3436673,3436242,3436019,3436668,3436136,3436673,3436242,3436019,3436668,3436136,3436673,3436242,3436091,3436668,3436136,3436673,3436242,3436091,3436668,3436136,3436673,3436466,3436099,3436668,3436136,3436673,3436466,3436099,3436868,3436136,3436673,3436466,3436107,3436868,3436136,3436673,3436786,3436107,3436868,3436136,3436673,3436786,3436115,3436868,3436136,3436673,3436786,3436115,3436988,3436136,3436673,3436988,3436136,3436673,3436988,3436136,3436673,3436988,3436136,3436673,3436136,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436144,3436144,3436144,3436144,3436144</t>
+          <t>3436136,3436019,3436242,3436019,3436668,3436136,3436019,3436242,3436019,3436668,3436136,3436091,3436242,3436091,3436668,3436136,3436091,3436242,3436091,3436668,3436136,3436099,3436466,3436099,3436668,3436136,3436099,3436466,3436099,3436868,3436136,3436107,3436466,3436107,3436868,3436136,3436107,3436786,3436107,3436868,3436136,3436115,3436786,3436115,3436868,3436136,3436115,3436786,3436115,3436988,3436136,3436673,3436988,3436136,3436673,3436988,3436136,3436673,3436988,3436136,3436673,3436136,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436673,3436144,3436144,3436144,3436144,3436144,3436144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L9 W9/25; N=87; EHP=1621.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x4,fast:58x3,medium:83x5,swarm:84x24,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L9 W9/25; N=87; EHP=3440.206101; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x4,fast:58x3,fast:98x3,medium:83x5,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3438136,3438673,3438242,3438019,3438668,3438136,3438673,3438242,3438019,3438668,3438136,3438673,3438242,3438091,3438668,3438136,3438673,3438466,3438091,3438668,3438136,3438673,3438466,3438099,3438868,3438136,3438673,3438466,3438099,3438868,3438136,3438673,3438466,3438107,3438868,3438136,3438673,3438786,3438107,3438868,3438136,3438673,3438786,3438107,3438988,3438136,3438673,3438786,3438115,3438988,3438136,3438673,3438786,3438115,3438988,3438136,3438673,3438988,3438136,3438673,3438988,3438136,3438673,3438136,3438673,3438136,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438144,3438144,3438144,3438144,3438144</t>
+          <t>3438136,3438019,3438242,3438019,3438668,3438136,3438019,3438242,3438019,3438668,3438136,3438091,3438242,3438091,3438668,3438136,3438091,3438466,3438091,3438668,3438136,3438099,3438466,3438099,3438868,3438136,3438099,3438466,3438099,3438868,3438136,3438107,3438466,3438107,3438868,3438136,3438107,3438786,3438107,3438868,3438136,3438107,3438786,3438107,3438988,3438136,3438115,3438786,3438115,3438988,3438136,3438115,3438786,3438115,3438988,3438136,3438673,3438988,3438136,3438673,3438988,3438136,3438673,3438136,3438673,3438136,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438673,3438144,3438144,3438144,3438144,3438144,3438144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L9 W10/25; N=93; EHP=2993.000000; air:2x2,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x16,normal:18x16,fast:30x3,fast:58x4,medium:83x4,swarm:84x26,fast:98x4,medium:108x4,medium:123x5</t>
+          <t>L9 W10/25; N=93; EHP=6355.128746; air:2x4,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x4,fast:98x4,medium:83x4,medium:108x4,medium:123x5,normal:17x16,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3440136,3440673,3440242,3440019,3440668,3440253,3440136,3440673,3440242,3440019,3440668,3440253,3440136,3440673,3440242,3440091,3440668,3440325,3440136,3440673,3440466,3440091,3440668,3440325,3440136,3440673,3440466,3440091,3440668,3440645,3440136,3440673,3440466,3440099,3440868,3440693,3440136,3440673,3440514,3440099,3440868,3440693,3440136,3440673,3440514,3440107,3440868,3440709,3440136,3440673,3440786,3440107,3440868,3441021,3440136,3440673,3440786,3440115,3440868,3440136,3440673,3440786,3440115,3440988,3440136,3440673,3440115,3440988,3440136,3440673,3440988,3440144,3440673,3440988,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440673</t>
+          <t>3440136,3440019,3440242,3440019,3440668,3440253,3440136,3440019,3440242,3440019,3440668,3440253,3440136,3440091,3440242,3440091,3440668,3440325,3440136,3440091,3440466,3440091,3440668,3440325,3440136,3440091,3440466,3440091,3440668,3440645,3440136,3440099,3440466,3440099,3440868,3440693,3440136,3440099,3440514,3440099,3440868,3440693,3440136,3440107,3440514,3440107,3440868,3440709,3440136,3440107,3440786,3440107,3440868,3441021,3440136,3440115,3440786,3440115,3440868,3440136,3440115,3440786,3440115,3440988,3440136,3440115,3440115,3440988,3440136,3440673,3440988,3440144,3440673,3440988,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440144,3440673,3440673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L9 W11/25; N=99; EHP=3053.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x3,normal:17x13,normal:18x13,fast:30x3,heavy:31x2,heavy:40x2,fast:58x3,fast:64x2,heavy:80x1,medium:83x5,swarm:84x27,heavy:86x2,heavy:88x1,fast:98x3,medium:108x5,medium:123x4,heavy:127x1</t>
+          <t>L9 W11/25; N=99; EHP=6475.364360; air:2x4,air:11x6,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x2,fast:98x3,heavy:31x2,heavy:40x2,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x5,medium:108x5,medium:123x4,normal:17x13,normal:18x13,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3442136,3442673,3442242,3442019,3442668,3442253,3442136,3442673,3442242,3442019,3442668,3442253,3442136,3442673,3442242,3442019,3442668,3442325,3442136,3442673,3442466,3442091,3442668,3442325,3442136,3442673,3442466,3442091,3442668,3442645,3442136,3442673,3442466,3442099,3442868,3442693,3442136,3442673,3442514,3442099,3442868,3442709,3442136,3442673,3442514,3442099,3442868,3442709,3442136,3442673,3442514,3442107,3442868,3443021,3442136,3442673,3442786,3442107,3442868,3443021,3442136,3442673,3442786,3442115,3442988,3442136,3442673,3442786,3442115,3442988,3442136,3442673,3442115,3442988,3442144,3442673,3442988,3442144,3442673,3442988,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442673,3442673,3442673</t>
+          <t>3442136,3442019,3442242,3442019,3442668,3442253,3442136,3442019,3442242,3442019,3442668,3442253,3442136,3442019,3442242,3442019,3442668,3442325,3442136,3442091,3442466,3442091,3442668,3442325,3442136,3442091,3442466,3442091,3442668,3442645,3442136,3442099,3442466,3442099,3442868,3442693,3442136,3442099,3442514,3442099,3442868,3442709,3442136,3442099,3442514,3442099,3442868,3442709,3442136,3442107,3442514,3442107,3442868,3443021,3442136,3442107,3442786,3442107,3442868,3443021,3442136,3442115,3442786,3442115,3442988,3442136,3442115,3442786,3442115,3442988,3442136,3442115,3442115,3442988,3442144,3442673,3442988,3442144,3442673,3442988,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442144,3442673,3442673,3442673,3442673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L9 W12/25; N=105; EHP=3160.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x13,fast:30x3,heavy:31x2,heavy:40x2,fast:58x3,fast:64x3,heavy:80x1,medium:83x5,swarm:84x29,heavy:86x1,heavy:88x2,fast:98x3,medium:108x5,medium:123x5,heavy:127x2</t>
+          <t>L9 W12/25; N=105; EHP=6703.742947; air:2x6,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x2,heavy:40x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x5,medium:108x5,medium:123x5,normal:17x13,normal:18x13,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3444136,3444673,3444242,3444019,3444668,3444253,3444136,3444673,3444242,3444019,3444668,3444325,3444136,3444673,3444242,3444019,3444668,3444325,3444136,3444673,3444466,3444091,3444668,3444645,3444136,3444673,3444466,3444091,3444668,3444645,3444136,3444673,3444466,3444099,3444868,3444693,3444136,3444673,3444466,3444099,3444868,3444693,3444136,3444673,3444514,3444099,3444868,3444709,3444136,3444673,3444514,3444107,3444868,3444709,3444136,3444673,3444514,3444107,3444868,3445021,3444136,3444673,3444786,3444107,3444988,3445021,3444136,3444673,3444786,3444115,3444988,3444136,3444673,3444786,3444115,3444988,3444144,3444673,3444988,3444144,3444673,3444988,3444144,3444673,3444988,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444673,3444673,3444673,3444673</t>
+          <t>3444136,3444019,3444242,3444019,3444668,3444253,3444136,3444019,3444242,3444019,3444668,3444325,3444136,3444019,3444242,3444019,3444668,3444325,3444136,3444091,3444466,3444091,3444668,3444645,3444136,3444091,3444466,3444091,3444668,3444645,3444136,3444099,3444466,3444099,3444868,3444693,3444136,3444099,3444466,3444099,3444868,3444693,3444136,3444099,3444514,3444099,3444868,3444709,3444136,3444107,3444514,3444107,3444868,3444709,3444136,3444107,3444514,3444107,3444868,3445021,3444136,3444107,3444786,3444107,3444988,3445021,3444136,3444115,3444786,3444115,3444988,3444136,3444115,3444786,3444115,3444988,3444144,3444673,3444988,3444144,3444673,3444988,3444144,3444673,3444988,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444144,3444673,3444673,3444673,3444673,3444673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L9 W13/25; N=111; EHP=3856.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x2,normal:17x13,normal:18x14,fast:30x3,heavy:31x1,heavy:40x2,fast:58x4,fast:64x3,heavy:80x2,medium:83x5,swarm:84x31,heavy:86x2,heavy:88x2,fast:98x3,medium:108x5,medium:123x6,heavy:127x2</t>
+          <t>L9 W13/25; N=111; EHP=8174.343852; air:2x6,air:11x4,air:12x6,air:13x6,air:14x4,fast:30x3,fast:58x4,fast:64x3,fast:98x3,heavy:31x1,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x5,medium:108x5,medium:123x6,normal:17x13,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3446136,3446673,3446242,3446019,3446668,3446253,3446136,3446673,3446242,3446019,3446668,3446253,3446136,3446673,3446242,3446019,3446668,3446325,3446136,3446673,3446242,3446091,3446668,3446645,3446136,3446673,3446466,3446091,3446668,3446645,3446136,3446673,3446466,3446091,3446668,3446693,3446136,3446673,3446466,3446099,3446868,3446693,3446136,3446673,3446514,3446099,3446868,3446709,3446136,3446673,3446514,3446107,3446868,3446709,3446136,3446673,3446514,3446107,3446868,3447021,3446136,3446673,3446514,3446107,3446868,3447021,3446136,3446673,3446786,3446115,3446868,3446136,3446673,3446786,3446115,3446988,3446136,3446673,3446786,3446115,3446988,3446136,3446673,3446988,3446144,3446673,3446988,3446144,3446673,3446988,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446673,3446673,3446673</t>
+          <t>3446136,3446019,3446242,3446019,3446668,3446253,3446136,3446019,3446242,3446019,3446668,3446253,3446136,3446019,3446242,3446019,3446668,3446325,3446136,3446091,3446242,3446091,3446668,3446645,3446136,3446091,3446466,3446091,3446668,3446645,3446136,3446091,3446466,3446091,3446668,3446693,3446136,3446099,3446466,3446099,3446868,3446693,3446136,3446099,3446514,3446099,3446868,3446709,3446136,3446107,3446514,3446107,3446868,3446709,3446136,3446107,3446514,3446107,3446868,3447021,3446136,3446107,3446514,3446107,3446868,3447021,3446136,3446115,3446786,3446115,3446868,3446136,3446115,3446786,3446115,3446988,3446136,3446115,3446786,3446115,3446988,3446136,3446673,3446988,3446144,3446673,3446988,3446144,3446673,3446988,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446144,3446673,3446673,3446673,3446673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L9 W14/25; N=117; EHP=4654.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x15,normal:18x14,fast:30x4,heavy:31x2,heavy:40x1,fast:58x3,fast:64x4,heavy:80x2,medium:83x6,swarm:84x32,heavy:86x2,heavy:88x2,fast:98x3,medium:108x6,medium:123x5,heavy:127x2</t>
+          <t>L9 W14/25; N=117; EHP=9868.956837; air:2x6,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x3,heavy:31x2,heavy:40x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x6,medium:108x6,medium:123x5,normal:17x15,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3448136,3448673,3448242,3448019,3448668,3448253,3449022,3448136,3448673,3448242,3448019,3448668,3448253,3448136,3448673,3448242,3448019,3448668,3448325,3448136,3448673,3448242,3448091,3448668,3448325,3448136,3448673,3448466,3448091,3448668,3448645,3448136,3448673,3448466,3448091,3448668,3448645,3448136,3448673,3448466,3448099,3448868,3448693,3448136,3448673,3448514,3448099,3448868,3448693,3448136,3448673,3448514,3448099,3448868,3448709,3448136,3448673,3448514,3448107,3448868,3448709,3448136,3448673,3448786,3448107,3448868,3449021,3448136,3448673,3448786,3448107,3448868,3449021,3448136,3448673,3448786,3448115,3448988,3448136,3448673,3448786,3448115,3448988,3448144,3448673,3448115,3448988,3448144,3448673,3448988,3448144,3448673,3448988,3448144,3448673,3448988,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448673,3448673,3448673,3448673,3448673</t>
+          <t>3448136,3448019,3448242,3448019,3448668,3448253,3449022,3448136,3448019,3448242,3448019,3448668,3448253,3448136,3448019,3448242,3448019,3448668,3448325,3448136,3448091,3448242,3448091,3448668,3448325,3448136,3448091,3448466,3448091,3448668,3448645,3448136,3448091,3448466,3448091,3448668,3448645,3448136,3448099,3448466,3448099,3448868,3448693,3448136,3448099,3448514,3448099,3448868,3448693,3448136,3448099,3448514,3448099,3448868,3448709,3448136,3448107,3448514,3448107,3448868,3448709,3448136,3448107,3448786,3448107,3448868,3449021,3448136,3448107,3448786,3448107,3448868,3449021,3448136,3448115,3448786,3448115,3448988,3448136,3448115,3448786,3448115,3448988,3448144,3448115,3448115,3448988,3448144,3448673,3448988,3448144,3448673,3448988,3448144,3448673,3448988,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448144,3448673,3448673,3448673,3448673,3448673,3448673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L9 W15/25; N=123; EHP=8123.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x4,heavy:31x2,heavy:40x2,fast:58x3,fast:64x3,heavy:80x2,medium:83x6,swarm:84x34,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,elite:127x1,heavy:127x2</t>
+          <t>L9 W15/25; N=123; EHP=17222.389412; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,elite:127x1,fast:30x4,fast:58x3,fast:64x3,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3450136,3450673,3450242,3450019,3450668,3450253,3450136,3450673,3450242,3450019,3450668,3450253,3450136,3450673,3450242,3450019,3450668,3450325,3450136,3450673,3450466,3450091,3450668,3450325,3450136,3450673,3450466,3450091,3450668,3450645,3450136,3450673,3450466,3450091,3450668,3450645,3450136,3450673,3450466,3450099,3450868,3450693,3450136,3450673,3450514,3450099,3450868,3450693,3450136,3450673,3450514,3450099,3450868,3450709,3450136,3450673,3450514,3450107,3450868,3450709,3450136,3450673,3450514,3450107,3450868,3451021,3450136,3450673,3450786,3450107,3450868,3451021,3450136,3450673,3450786,3450115,3450988,3450136,3450673,3450786,3450115,3450988,3450136,3450673,3450786,3450115,3450988,3450136,3450673,3450988,3450144,3450673,3450988,3450144,3450673,3450988,3450144,3450673,3450988,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450673,3450673,3450673,3450673</t>
+          <t>3450136,3450019,3450242,3450019,3450668,3450253,3450136,3450019,3450242,3450019,3450668,3450253,3450136,3450019,3450242,3450019,3450668,3450325,3450136,3450091,3450466,3450091,3450668,3450325,3450136,3450091,3450466,3450091,3450668,3450645,3450136,3450091,3450466,3450091,3450668,3450645,3450136,3450099,3450466,3450099,3450868,3450693,3450136,3450099,3450514,3450099,3450868,3450693,3450136,3450099,3450514,3450099,3450868,3450709,3450136,3450107,3450514,3450107,3450868,3450709,3450136,3450107,3450514,3450107,3450868,3451021,3450136,3450107,3450786,3450107,3450868,3451021,3450136,3450115,3450786,3450115,3450988,3450136,3450115,3450786,3450115,3450988,3450136,3450115,3450786,3450115,3450988,3450136,3450673,3450988,3450144,3450673,3450988,3450144,3450673,3450988,3450144,3450673,3450988,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450144,3450673,3450673,3450673,3450673,3450673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L9 W16/25; N=129; EHP=8286.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:80x2,medium:83x6,swarm:84x36,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x7,heavy:127x2</t>
+          <t>L9 W16/25; N=129; EHP=17564.943003; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x6,medium:108x6,medium:123x7,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3452136,3452673,3452242,3452019,3452668,3452253,3452136,3452673,3452242,3452019,3452668,3452253,3452136,3452673,3452242,3452019,3452668,3452325,3452136,3452673,3452242,3452091,3452668,3452325,3452136,3452673,3452466,3452091,3452668,3452645,3452136,3452673,3452466,3452091,3452668,3452645,3452136,3452673,3452466,3452099,3452668,3452693,3452136,3452673,3452466,3452099,3452868,3452693,3452136,3452673,3452514,3452099,3452868,3452693,3452136,3452673,3452514,3452107,3452868,3452709,3452136,3452673,3452514,3452107,3452868,3452709,3452136,3452673,3452514,3452107,3452868,3453021,3452136,3452673,3452786,3452115,3452868,3453021,3452136,3452673,3452786,3452115,3452868,3452136,3452673,3452786,3452115,3452988,3452136,3452673,3452786,3452115,3452988,3452144,3452673,3452988,3452144,3452673,3452988,3452144,3452673,3452988,3452144,3452673,3452988,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452673,3452673,3452673,3452673</t>
+          <t>3452136,3452019,3452242,3452019,3452668,3452253,3452136,3452019,3452242,3452019,3452668,3452253,3452136,3452019,3452242,3452019,3452668,3452325,3452136,3452091,3452242,3452091,3452668,3452325,3452136,3452091,3452466,3452091,3452668,3452645,3452136,3452091,3452466,3452091,3452668,3452645,3452136,3452099,3452466,3452099,3452668,3452693,3452136,3452099,3452466,3452099,3452868,3452693,3452136,3452099,3452514,3452099,3452868,3452693,3452136,3452107,3452514,3452107,3452868,3452709,3452136,3452107,3452514,3452107,3452868,3452709,3452136,3452107,3452514,3452107,3452868,3453021,3452136,3452115,3452786,3452115,3452868,3453021,3452136,3452115,3452786,3452115,3452868,3452136,3452115,3452786,3452115,3452988,3452136,3452115,3452786,3452115,3452988,3452144,3452673,3452988,3452144,3452673,3452988,3452144,3452673,3452988,3452144,3452673,3452988,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452144,3452673,3452673,3452673,3452673,3452673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L9 W17/25; N=135; EHP=8452.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x4,normal:17x16,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:80x2,medium:83x7,swarm:84x37,heavy:86x3,heavy:88x2,fast:98x4,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L9 W17/25; N=135; EHP=17919.748410; air:2x6,air:11x6,air:12x6,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x6,normal:17x16,normal:18x17,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3454136,3454673,3454242,3454019,3454668,3454253,3454136,3454673,3454242,3454019,3454668,3454253,3454136,3454673,3454242,3454019,3454668,3454253,3454136,3454673,3454242,3454019,3454668,3454325,3454136,3454673,3454466,3454091,3454668,3454325,3454136,3454673,3454466,3454091,3454668,3454325,3454136,3454673,3454466,3454091,3454668,3454645,3454136,3454673,3454466,3454099,3454868,3454645,3454136,3454673,3454514,3454099,3454868,3454693,3454136,3454673,3454514,3454099,3454868,3454693,3454136,3454673,3454514,3454099,3454868,3454709,3454136,3454673,3454514,3454107,3454868,3454709,3454136,3454673,3454786,3454107,3454868,3455021,3454136,3454673,3454786,3454107,3454868,3455021,3454136,3454673,3454786,3454115,3454988,3454136,3454673,3454786,3454115,3454988,3454136,3454673,3454115,3454988,3454144,3454673,3454988,3454144,3454673,3454988,3454144,3454673,3454988,3454144,3454673,3454988,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454673,3454673,3454673,3454673,3454673</t>
+          <t>3454136,3454019,3454242,3454019,3454668,3454253,3454136,3454019,3454242,3454019,3454668,3454253,3454136,3454019,3454242,3454019,3454668,3454253,3454136,3454019,3454242,3454019,3454668,3454325,3454136,3454091,3454466,3454091,3454668,3454325,3454136,3454091,3454466,3454091,3454668,3454325,3454136,3454091,3454466,3454091,3454668,3454645,3454136,3454099,3454466,3454099,3454868,3454645,3454136,3454099,3454514,3454099,3454868,3454693,3454136,3454099,3454514,3454099,3454868,3454693,3454136,3454099,3454514,3454099,3454868,3454709,3454136,3454107,3454514,3454107,3454868,3454709,3454136,3454107,3454786,3454107,3454868,3455021,3454136,3454107,3454786,3454107,3454868,3455021,3454136,3454115,3454786,3454115,3454988,3454136,3454115,3454786,3454115,3454988,3454136,3454115,3454115,3454988,3454144,3454673,3454988,3454144,3454673,3454988,3454144,3454673,3454988,3454144,3454673,3454988,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454144,3454673,3454673,3454673,3454673,3454673,3454673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L9 W18/25; N=141; EHP=9032.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x17,normal:18x17,fast:30x4,heavy:31x3,heavy:40x3,fast:58x4,fast:64x4,heavy:80x2,medium:83x7,swarm:84x39,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L9 W18/25; N=141; EHP=19152.572388; air:2x8,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x3,heavy:40x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3456136,3456673,3456242,3456019,3456668,3456253,3456136,3456673,3456242,3456019,3456668,3456253,3456136,3456673,3456242,3456019,3456668,3456325,3456136,3456673,3456242,3456019,3456668,3456325,3456136,3456673,3456242,3456091,3456668,3456325,3456136,3456673,3456466,3456091,3456668,3456645,3456136,3456673,3456466,3456091,3456668,3456645,3456136,3456673,3456466,3456091,3456868,3456693,3456136,3456673,3456466,3456099,3456868,3456693,3456136,3456673,3456514,3456099,3456868,3456709,3456136,3456673,3456514,3456099,3456868,3456709,3456136,3456673,3456514,3456107,3456868,3457021,3456136,3456673,3456514,3456107,3456868,3457021,3456136,3456673,3456786,3456107,3456868,3457021,3456136,3456673,3456786,3456107,3456988,3456136,3456673,3456786,3456115,3456988,3456136,3456673,3456786,3456115,3456988,3456144,3456673,3456115,3456988,3456144,3456673,3456988,3456144,3456673,3456988,3456144,3456673,3456988,3456144,3456673,3456988,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456673,3456673,3456673,3456673,3456673,3456673</t>
+          <t>3456136,3456019,3456242,3456019,3456668,3456253,3456136,3456019,3456242,3456019,3456668,3456253,3456136,3456019,3456242,3456019,3456668,3456325,3456136,3456019,3456242,3456019,3456668,3456325,3456136,3456091,3456242,3456091,3456668,3456325,3456136,3456091,3456466,3456091,3456668,3456645,3456136,3456091,3456466,3456091,3456668,3456645,3456136,3456091,3456466,3456091,3456868,3456693,3456136,3456099,3456466,3456099,3456868,3456693,3456136,3456099,3456514,3456099,3456868,3456709,3456136,3456099,3456514,3456099,3456868,3456709,3456136,3456107,3456514,3456107,3456868,3457021,3456136,3456107,3456514,3456107,3456868,3457021,3456136,3456107,3456786,3456107,3456868,3457021,3456136,3456107,3456786,3456107,3456988,3456136,3456115,3456786,3456115,3456988,3456136,3456115,3456786,3456115,3456988,3456144,3456115,3456115,3456988,3456144,3456673,3456988,3456144,3456673,3456988,3456144,3456673,3456988,3456144,3456673,3456988,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456144,3456673,3456673,3456673,3456673,3456673,3456673,3456673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L9 W19/25; N=147; EHP=10460.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x17,normal:18x18,fast:30x5,heavy:31x2,heavy:40x3,fast:58x4,fast:64x4,heavy:80x2,medium:83x7,swarm:84x41,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x8,heavy:127x3</t>
+          <t>L9 W19/25; N=147; EHP=22186.255817; air:2x8,air:11x8,air:12x6,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x7,medium:108x7,medium:123x8,normal:17x17,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3458136,3458673,3458242,3458019,3458668,3458253,3459022,3458136,3458673,3458242,3458019,3458668,3458253,3458136,3458673,3458242,3458019,3458668,3458325,3458136,3458673,3458242,3458091,3458668,3458325,3458136,3458673,3458466,3458091,3458668,3458645,3458136,3458673,3458466,3458091,3458668,3458645,3458136,3458673,3458466,3458091,3458668,3458645,3458136,3458673,3458466,3458099,3458868,3458693,3458136,3458673,3458466,3458099,3458868,3458693,3458136,3458673,3458514,3458099,3458868,3458709,3458136,3458673,3458514,3458107,3458868,3458709,3458136,3458673,3458514,3458107,3458868,3458709,3458136,3458673,3458514,3458107,3458868,3459021,3458136,3458673,3458786,3458107,3458868,3459021,3458136,3458673,3458786,3458115,3458868,3459021,3458136,3458673,3458786,3458115,3458988,3458136,3458673,3458786,3458115,3458988,3458136,3458673,3458786,3458115,3458988,3458136,3458673,3458988,3458144,3458673,3458988,3458144,3458673,3458988,3458144,3458673,3458988,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458673,3458673,3458673,3458673,3458673</t>
+          <t>3458136,3458019,3458242,3458019,3458668,3458253,3459022,3458136,3458019,3458242,3458019,3458668,3458253,3458136,3458019,3458242,3458019,3458668,3458325,3458136,3458091,3458242,3458091,3458668,3458325,3458136,3458091,3458466,3458091,3458668,3458645,3458136,3458091,3458466,3458091,3458668,3458645,3458136,3458091,3458466,3458091,3458668,3458645,3458136,3458099,3458466,3458099,3458868,3458693,3458136,3458099,3458466,3458099,3458868,3458693,3458136,3458099,3458514,3458099,3458868,3458709,3458136,3458107,3458514,3458107,3458868,3458709,3458136,3458107,3458514,3458107,3458868,3458709,3458136,3458107,3458514,3458107,3458868,3459021,3458136,3458107,3458786,3458107,3458868,3459021,3458136,3458115,3458786,3458115,3458868,3459021,3458136,3458115,3458786,3458115,3458988,3458136,3458115,3458786,3458115,3458988,3458136,3458115,3458786,3458115,3458988,3458136,3458673,3458988,3458144,3458673,3458988,3458144,3458673,3458988,3458144,3458673,3458988,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458144,3458673,3458673,3458673,3458673,3458673,3458673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L9 W20/25; N=153; EHP=17566.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x19,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:80x3,medium:83x7,swarm:84x42,heavy:86x2,heavy:88x3,fast:98x5,medium:108x8,medium:123x7,elite:127x1,heavy:127x3</t>
+          <t>L9 W20/25; N=153; EHP=37230.452812; air:2x6,air:11x8,air:12x6,air:13x8,air:14x8,elite:127x1,fast:30x4,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x3,medium:83x7,medium:108x8,medium:123x7,normal:17x19,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10017310,10017319,10017312,10048550,10017318,10017313,10017310,10017319,10017312,10048550,10017318,10017313,10017310,10017319,10017312,10048550,10017318,10017314,10017310,10017319,10017312,10048550,10017318,10017314,10017310,10017319,10017312,10017307,10017318,10017317,10017310,10017319,10017315,10017307,10017318,10017317,10017310,10017319,10017315,10017307,10017318,10017317,10017310,10017319,10017315,10017307,10017318,10017320,10017310,10017319,10017315,10048551,10017323,10017320,10017310,10017319,10017315,10048551,10017323,10017320,10017310,10017319,10017316,10048551,10017323,10017321,10017310,10017319,10017316,10048551,10017323,10017321,10017310,10017319,10017316,10017308,10017323,10017321,10017310,10017319,10017316,10017308,10017323,10017325,10017310,10017319,10017316,10017308,10017323,10017325,10017310,10017319,10017322,10017309,10017324,10017310,10017319,10017322,10017309,10017324,10017310,10017319,10017322,10017309,10017324,10017310,10017319,10017322,10017309,10017324,10017311,10017319,10017324,10017311,10017319,10017324,10017311,10017319,10017324,10017311,10017319,10017324,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017319,10017319,10017319,10017319,10017319</t>
+          <t>10017310,10048550,10017312,10048550,10017318,10017313,10017310,10048550,10017312,10048550,10017318,10017313,10017310,10048550,10017312,10048550,10017318,10017314,10017310,10048550,10017312,10048550,10017318,10017314,10017310,10017307,10017312,10017307,10017318,10017317,10017310,10017307,10017315,10017307,10017318,10017317,10017310,10017307,10017315,10017307,10017318,10017317,10017310,10017307,10017315,10017307,10017318,10017320,10017310,10048551,10017315,10048551,10017323,10017320,10017310,10048551,10017315,10048551,10017323,10017320,10017310,10048551,10017316,10048551,10017323,10017321,10017310,10048551,10017316,10048551,10017323,10017321,10017310,10017308,10017316,10017308,10017323,10017321,10017310,10017308,10017316,10017308,10017323,10017325,10017310,10017308,10017316,10017308,10017323,10017325,10017310,10017309,10017322,10017309,10017324,10017310,10017309,10017322,10017309,10017324,10017310,10017309,10017322,10017309,10017324,10017310,10017309,10017322,10017309,10017324,10017311,10017319,10017324,10017311,10017319,10017324,10017311,10017319,10017324,10017311,10017319,10017324,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017311,10017319,10017319,10017319,10017319,10017319,10017319</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L9 W21/25; N=159; EHP=17918.000000; air:2x4,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:80x3,medium:83x8,swarm:84x44,heavy:86x3,heavy:88x3,fast:98x4,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L9 W21/25; N=159; EHP=37995.563809; air:2x8,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x3,heavy:86x3,heavy:88x3,heavy:127x2,medium:83x8,medium:108x7,medium:123x8,normal:17x19,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10017329,10017338,10017331,10048552,10017337,10017332,10017329,10017338,10017331,10048552,10017337,10017332,10017329,10017338,10017331,10048552,10017337,10017332,10017329,10017338,10017331,10048552,10017337,10017333,10017329,10017338,10017331,10017326,10017337,10017333,10017329,10017338,10017334,10017326,10017337,10017333,10017329,10017338,10017334,10017326,10017337,10017336,10017329,10017338,10017334,10017326,10017337,10017336,10017329,10017338,10017334,10048553,10017342,10017336,10017329,10017338,10017335,10048553,10017342,10017339,10017329,10017338,10017335,10048553,10017342,10017339,10017329,10017338,10017335,10048553,10017342,10017339,10017329,10017338,10017335,10017327,10017342,10017340,10017329,10017338,10017335,10017327,10017342,10017340,10017329,10017338,10017341,10017327,10017342,10017344,10017329,10017338,10017341,10017327,10017342,10017344,10017329,10017338,10017341,10017328,10017343,10017329,10017338,10017341,10017328,10017343,10017329,10017338,10017341,10017328,10017343,10017329,10017338,10017328,10017343,10017330,10017338,10017343,10017330,10017338,10017343,10017330,10017338,10017343,10017330,10017338,10017343,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017338,10017338,10017338,10017338,10017338,10017338</t>
+          <t>10017329,10048552,10017331,10048552,10017337,10017332,10017329,10048552,10017331,10048552,10017337,10017332,10017329,10048552,10017331,10048552,10017337,10017332,10017329,10048552,10017331,10048552,10017337,10017333,10017329,10017326,10017331,10017326,10017337,10017333,10017329,10017326,10017334,10017326,10017337,10017333,10017329,10017326,10017334,10017326,10017337,10017336,10017329,10017326,10017334,10017326,10017337,10017336,10017329,10048553,10017334,10048553,10017342,10017336,10017329,10048553,10017335,10048553,10017342,10017339,10017329,10048553,10017335,10048553,10017342,10017339,10017329,10048553,10017335,10048553,10017342,10017339,10017329,10017327,10017335,10017327,10017342,10017340,10017329,10017327,10017335,10017327,10017342,10017340,10017329,10017327,10017341,10017327,10017342,10017344,10017329,10017327,10017341,10017327,10017342,10017344,10017329,10017328,10017341,10017328,10017343,10017329,10017328,10017341,10017328,10017343,10017329,10017328,10017341,10017328,10017343,10017329,10017328,10017328,10017343,10017330,10017338,10017343,10017330,10017338,10017343,10017330,10017338,10017343,10017330,10017338,10017343,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017330,10017338,10017338,10017338,10017338,10017338,10017338,10017338</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L9 W22/25; N=165; EHP=18277.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x3,heavy:40x3,fast:58x4,fast:64x5,heavy:80x3,medium:83x8,swarm:84x46,heavy:86x3,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L9 W22/25; N=165; EHP=38762.016491; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x4,fast:64x5,fast:98x5,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017348,10017357,10017350,10048554,10017356,10017351,10017348,10017357,10017350,10048554,10017356,10017351,10017348,10017357,10017350,10048554,10017356,10017351,10017348,10017357,10017350,10048554,10017356,10017352,10017348,10017357,10017350,10017345,10017356,10017352,10017348,10017357,10017353,10017345,10017356,10017352,10017348,10017357,10017353,10017345,10017356,10017355,10017348,10017357,10017353,10017345,10017356,10017355,10017348,10017357,10017353,10048555,10017361,10017358,10017348,10017357,10017353,10048555,10017361,10017358,10017348,10017357,10017354,10048555,10017361,10017358,10017348,10017357,10017354,10048555,10017361,10017359,10017348,10017357,10017354,10048555,10017361,10017359,10017348,10017357,10017354,10017346,10017361,10017359,10017348,10017357,10017354,10017346,10017361,10017363,10017348,10017357,10017360,10017346,10017361,10017363,10017348,10017357,10017360,10017346,10017361,10017363,10017348,10017357,10017360,10017347,10017362,10017348,10017357,10017360,10017347,10017362,10017348,10017357,10017360,10017347,10017362,10017349,10017357,10017347,10017362,10017349,10017357,10017362,10017349,10017357,10017362,10017349,10017357,10017362,10017349,10017357,10017362,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017357,10017357,10017357,10017357,10017357,10017357</t>
+          <t>10017348,10048554,10017350,10048554,10017356,10017351,10017348,10048554,10017350,10048554,10017356,10017351,10017348,10048554,10017350,10048554,10017356,10017351,10017348,10048554,10017350,10048554,10017356,10017352,10017348,10017345,10017350,10017345,10017356,10017352,10017348,10017345,10017353,10017345,10017356,10017352,10017348,10017345,10017353,10017345,10017356,10017355,10017348,10017345,10017353,10017345,10017356,10017355,10017348,10048555,10017353,10048555,10017361,10017358,10017348,10048555,10017353,10048555,10017361,10017358,10017348,10048555,10017354,10048555,10017361,10017358,10017348,10048555,10017354,10048555,10017361,10017359,10017348,10048555,10017354,10048555,10017361,10017359,10017348,10017346,10017354,10017346,10017361,10017359,10017348,10017346,10017354,10017346,10017361,10017363,10017348,10017346,10017360,10017346,10017361,10017363,10017348,10017346,10017360,10017346,10017361,10017363,10017348,10017347,10017360,10017347,10017362,10017348,10017347,10017360,10017347,10017362,10017348,10017347,10017360,10017347,10017362,10017349,10017347,10017347,10017362,10017349,10017357,10017362,10017349,10017357,10017362,10017349,10017357,10017362,10017349,10017357,10017362,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017349,10017357,10017357,10017357,10017357,10017357,10017357,10017357</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L9 W23/25; N=171; EHP=18643.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x20,normal:18x21,fast:30x5,heavy:31x3,heavy:40x3,fast:58x5,fast:64x5,heavy:80x2,medium:83x8,swarm:84x47,heavy:86x3,heavy:88x3,fast:98x5,medium:108x9,medium:123x8,heavy:127x3</t>
+          <t>L9 W23/25; N=171; EHP=39542.605467; air:2x8,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x3,heavy:40x3,heavy:80x2,heavy:86x3,heavy:88x3,heavy:127x3,medium:83x8,medium:108x9,medium:123x8,normal:17x20,normal:18x21,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017367,10017376,10017369,10048556,10017375,10017370,10017367,10017376,10017369,10048556,10017375,10017370,10017367,10017376,10017369,10048556,10017375,10017370,10017367,10017376,10017369,10048556,10017375,10017371,10017367,10017376,10017369,10048556,10017375,10017371,10017367,10017376,10017372,10017364,10017375,10017371,10017367,10017376,10017372,10017364,10017375,10017374,10017367,10017376,10017372,10017364,10017375,10017374,10017367,10017376,10017372,10017364,10017375,10017374,10017367,10017376,10017372,10048557,10017380,10017377,10017367,10017376,10017373,10048557,10017380,10017377,10017367,10017376,10017373,10048557,10017380,10017378,10017367,10017376,10017373,10048557,10017380,10017378,10017367,10017376,10017373,10017365,10017380,10017378,10017367,10017376,10017373,10017365,10017380,10017382,10017367,10017376,10017379,10017365,10017380,10017382,10017367,10017376,10017379,10017365,10017380,10017382,10017367,10017376,10017379,10017366,10017381,10017367,10017376,10017379,10017366,10017381,10017367,10017376,10017379,10017366,10017381,10017367,10017376,10017379,10017366,10017381,10017367,10017376,10017381,10017368,10017376,10017381,10017368,10017376,10017381,10017368,10017376,10017381,10017368,10017376,10017381,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017376,10017376,10017376,10017376,10017376,10017376</t>
+          <t>10017367,10048556,10017369,10048556,10017375,10017370,10017367,10048556,10017369,10048556,10017375,10017370,10017367,10048556,10017369,10048556,10017375,10017370,10017367,10048556,10017369,10048556,10017375,10017371,10017367,10048556,10017369,10048556,10017375,10017371,10017367,10017364,10017372,10017364,10017375,10017371,10017367,10017364,10017372,10017364,10017375,10017374,10017367,10017364,10017372,10017364,10017375,10017374,10017367,10017364,10017372,10017364,10017375,10017374,10017367,10048557,10017372,10048557,10017380,10017377,10017367,10048557,10017373,10048557,10017380,10017377,10017367,10048557,10017373,10048557,10017380,10017378,10017367,10048557,10017373,10048557,10017380,10017378,10017367,10017365,10017373,10017365,10017380,10017378,10017367,10017365,10017373,10017365,10017380,10017382,10017367,10017365,10017379,10017365,10017380,10017382,10017367,10017365,10017379,10017365,10017380,10017382,10017367,10017366,10017379,10017366,10017381,10017367,10017366,10017379,10017366,10017381,10017367,10017366,10017379,10017366,10017381,10017367,10017366,10017379,10017366,10017381,10017367,10017376,10017381,10017368,10017376,10017381,10017368,10017376,10017381,10017368,10017376,10017381,10017368,10017376,10017381,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017368,10017376,10017376,10017376,10017376,10017376,10017376,10017376</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L9 W24/25; N=177; EHP=19962.000000; air:2x5,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x22,normal:18x21,fast:30x5,heavy:31x3,heavy:40x3,fast:58x5,fast:64x5,heavy:80x3,medium:83x9,swarm:84x49,heavy:86x2,heavy:88x3,fast:98x6,medium:108x8,medium:123x9,heavy:127x3</t>
+          <t>L9 W24/25; N=177; EHP=42324.534859; air:2x10,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x6,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x3,medium:83x9,medium:108x8,medium:123x9,normal:17x22,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017386,10017395,10017388,10048558,10017394,10017389,10017400,10017386,10017395,10017388,10048558,10017394,10017389,10017386,10017395,10017388,10048558,10017394,10017389,10017386,10017395,10017388,10048558,10017394,10017390,10017386,10017395,10017388,10017383,10017394,10017390,10017386,10017395,10017391,10017383,10017394,10017390,10017386,10017395,10017391,10017383,10017394,10017393,10017386,10017395,10017391,10017383,10017394,10017393,10017386,10017395,10017391,10017383,10017394,10017393,10017386,10017395,10017391,10048559,10017399,10017396,10017386,10017395,10017391,10048559,10017399,10017396,10017386,10017395,10017392,10048559,10017399,10017396,10017386,10017395,10017392,10048559,10017399,10017397,10017386,10017395,10017392,10017384,10017399,10017397,10017386,10017395,10017392,10017384,10017399,10017397,10017386,10017395,10017392,10017384,10017399,10017402,10017386,10017395,10017398,10017384,10017399,10017402,10017386,10017395,10017398,10017384,10017399,10017402,10017386,10017395,10017398,10017385,10017401,10017386,10017395,10017398,10017385,10017401,10017386,10017395,10017398,10017385,10017401,10017387,10017395,10017385,10017401,10017387,10017395,10017401,10017387,10017395,10017401,10017387,10017395,10017401,10017387,10017395,10017401,10017387,10017395,10017401,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017395,10017395,10017395,10017395,10017395,10017395,10017395,10017395</t>
+          <t>10017386,10048558,10017388,10048558,10017394,10017389,10017400,10017386,10048558,10017388,10048558,10017394,10017389,10017386,10048558,10017388,10048558,10017394,10017389,10017386,10048558,10017388,10048558,10017394,10017390,10017386,10017383,10017388,10017383,10017394,10017390,10017386,10017383,10017391,10017383,10017394,10017390,10017386,10017383,10017391,10017383,10017394,10017393,10017386,10017383,10017391,10017383,10017394,10017393,10017386,10017383,10017391,10017383,10017394,10017393,10017386,10048559,10017391,10048559,10017399,10017396,10017386,10048559,10017391,10048559,10017399,10017396,10017386,10048559,10017392,10048559,10017399,10017396,10017386,10048559,10017392,10048559,10017399,10017397,10017386,10017384,10017392,10017384,10017399,10017397,10017386,10017384,10017392,10017384,10017399,10017397,10017386,10017384,10017392,10017384,10017399,10017402,10017386,10017384,10017398,10017384,10017399,10017402,10017386,10017384,10017398,10017384,10017399,10017402,10017386,10017385,10017398,10017385,10017401,10017386,10017385,10017398,10017385,10017401,10017386,10017385,10017398,10017385,10017401,10017387,10017385,10017385,10017401,10017387,10017395,10017401,10017387,10017395,10017401,10017387,10017395,10017401,10017387,10017395,10017401,10017387,10017395,10017401,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017387,10017395,10017395,10017395,10017395,10017395,10017395,10017395,10017395,10017395</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L9 W25/25; N=183; EHP=39848.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x21,normal:18x22,fast:30x5,heavy:31x3,heavy:40x3,fast:58x6,fast:64x5,heavy:80x3,medium:83x9,swarm:84x51,heavy:86x3,heavy:88x3,fast:98x5,medium:108x9,elite:123x1,medium:123x9,heavy:127x3</t>
+          <t>L9 W25/25; N=183; EHP=84479.573308; air:2x8,air:11x10,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x5,fast:58x6,fast:64x5,fast:98x5,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x3,heavy:127x3,medium:83x9,medium:108x9,medium:123x9,normal:17x21,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L09/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L09/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>243</v>
+        <v>330</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>208</v>
+        <v>340</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>194</v>
+        <v>290</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>173</v>
+        <v>260</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>159</v>
+        <v>330</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>152</v>
+        <v>250</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>145</v>
+        <v>280</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
